--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106288</v>
+        <v>106308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106319</v>
+        <v>106330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106330</v>
+        <v>106343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106343</v>
+        <v>106344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106344</v>
+        <v>106357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22512-2024 artfynd.xlsx
+++ b/artfynd/A 22512-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135951300</v>
       </c>
       <c r="B2" t="n">
-        <v>106357</v>
+        <v>106358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
